--- a/tower28beauty/tower28beauty_5_upgraded_products.xlsx
+++ b/tower28beauty/tower28beauty_5_upgraded_products.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -160,6 +160,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -531,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,35 +571,45 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Current Word Count</t>
+          <t>Feed Word Count (Shopify API)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Live Storefront Words (Theme)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Diagnostic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Upgraded Description (Clean Readable Text + Specs)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Current Alt Text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Image Alt Text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Google Shopping Category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Smart Tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Live Product URL</t>
         </is>
@@ -628,7 +639,15 @@
       <c r="E2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>The Off-Duty Complexion Trio by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -640,27 +659,27 @@
 ApplicationMorning &amp; Evening Daily RegimenSkin TypesSuitable for all skin types, including sensitiveKey BenefitDeep hydration, barrier repair, and radiant balanceBrand OriginTower28Beauty (United States)Quality GuaranteeClean, Non-Toxic, Dermatologist-Approved</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Off-Duty Complexion Trio - Tower28Beauty Official Product View</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>Clean Beauty, Skincare Essentials, Daily Ritual, Cruelty-Free, Dermatologist-Approved, Made in USA</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>https://tower28beauty.com/products/off-duty-complexion-trio</t>
         </is>
@@ -690,7 +709,15 @@
       <c r="E3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="7" t="n">
+        <v>904</v>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>The Wink + Wave Mini Duo by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -702,27 +729,27 @@
 ApplicationMorning &amp; Evening Daily RegimenSkin TypesSuitable for all skin types, including sensitiveKey BenefitDeep hydration, barrier repair, and radiant balanceBrand OriginTower28Beauty (United States)Quality GuaranteeClean, Non-Toxic, Dermatologist-Approved</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Wink + Wave Mini Duo - Tower28Beauty Official Product View</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>Clean Beauty, Skincare Essentials, Daily Ritual, Cruelty-Free, Dermatologist-Approved, Made in USA</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>https://tower28beauty.com/products/wink-wave-mini-duo</t>
         </is>
@@ -752,7 +779,15 @@
       <c r="E4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="n">
+        <v>1769</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>The The Fresh Face Set by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -764,27 +799,27 @@
 ApplicationMorning &amp; Evening Daily RegimenSkin TypesSuitable for all skin types, including sensitiveKey BenefitDeep hydration, barrier repair, and radiant balanceBrand OriginTower28Beauty (United States)Quality GuaranteeClean, Non-Toxic, Dermatologist-Approved</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>The Fresh Face Set - Tower28Beauty Official Product View</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>Clean Beauty, Skincare Essentials, Daily Ritual, Cruelty-Free, Dermatologist-Approved, Made in USA</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>https://tower28beauty.com/products/the-fresh-face-set</t>
         </is>
@@ -814,7 +849,15 @@
       <c r="E5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>The JELL-O® x TOWER 28 RED SHINE-ON BAG by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -826,27 +869,27 @@
 ApplicationMorning &amp; Evening Daily RegimenSkin TypesSuitable for all skin types, including sensitiveKey BenefitDeep hydration, barrier repair, and radiant balanceBrand OriginTower28Beauty (United States)Quality GuaranteeClean, Non-Toxic, Dermatologist-Approved</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>JELL-O® x TOWER 28 RED SHINE-ON BAG - Tower28Beauty Official Product View</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>Clean Beauty, Skincare Essentials, Daily Ritual, Cruelty-Free, Dermatologist-Approved, Made in USA</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>https://tower28beauty.com/products/jell-o-x-tower-28-red-shine-on-bag</t>
         </is>
@@ -876,7 +919,15 @@
       <c r="E6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="n">
+        <v>605</v>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>The So Juicy JELL-O® x Tower 28 Bag Charm by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -888,27 +939,27 @@
 ApplicationMorning &amp; Evening Daily RegimenSkin TypesSuitable for all skin types, including sensitiveKey BenefitDeep hydration, barrier repair, and radiant balanceBrand OriginTower28Beauty (United States)Quality GuaranteeClean, Non-Toxic, Dermatologist-Approved</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>So Juicy JELL-O® x Tower 28 Bag Charm - Tower28Beauty Official Product View</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>Clean Beauty, Skincare Essentials, Daily Ritual, Cruelty-Free, Dermatologist-Approved, Made in USA</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>https://tower28beauty.com/products/so-juicy-jell-o®-x-tower-28-bag-charm</t>
         </is>
@@ -967,164 +1018,164 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Handle</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Body (HTML)</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Option1 Name</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Option1 Value</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Variant SKU</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>Variant Grams</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Tracker</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Qty</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Policy</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="P1" s="11" t="inlineStr">
         <is>
           <t>Variant Fulfillment Service</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="Q1" s="11" t="inlineStr">
         <is>
           <t>Variant Price</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="R1" s="11" t="inlineStr">
         <is>
           <t>Variant Compare At Price</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="S1" s="11" t="inlineStr">
         <is>
           <t>Variant Requires Shipping</t>
         </is>
       </c>
-      <c r="T1" s="10" t="inlineStr">
+      <c r="T1" s="11" t="inlineStr">
         <is>
           <t>Variant Taxable</t>
         </is>
       </c>
-      <c r="U1" s="10" t="inlineStr">
+      <c r="U1" s="11" t="inlineStr">
         <is>
           <t>Variant Barcode</t>
         </is>
       </c>
-      <c r="V1" s="10" t="inlineStr">
+      <c r="V1" s="11" t="inlineStr">
         <is>
           <t>Image Src</t>
         </is>
       </c>
-      <c r="W1" s="10" t="inlineStr">
+      <c r="W1" s="11" t="inlineStr">
         <is>
           <t>Image Position</t>
         </is>
       </c>
-      <c r="X1" s="10" t="inlineStr">
+      <c r="X1" s="11" t="inlineStr">
         <is>
           <t>Image Alt Text</t>
         </is>
       </c>
-      <c r="Y1" s="10" t="inlineStr">
+      <c r="Y1" s="11" t="inlineStr">
         <is>
           <t>Gift Card</t>
         </is>
       </c>
-      <c r="Z1" s="10" t="inlineStr">
+      <c r="Z1" s="11" t="inlineStr">
         <is>
           <t>SEO Title</t>
         </is>
       </c>
-      <c r="AA1" s="10" t="inlineStr">
+      <c r="AA1" s="11" t="inlineStr">
         <is>
           <t>SEO Description</t>
         </is>
       </c>
-      <c r="AB1" s="10" t="inlineStr">
+      <c r="AB1" s="11" t="inlineStr">
         <is>
           <t>Google Shopping / Google Product Category</t>
         </is>
       </c>
-      <c r="AC1" s="10" t="inlineStr">
+      <c r="AC1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>off-duty-complexion-trio</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Off-Duty Complexion Trio | Restorative Daily Formula</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Off-Duty Complexion Trio&lt;/strong&gt; by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1139,141 +1190,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Tower28Beauty</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>Clean Beauty, Skincare Essentials, Daily Ritual, Cruelty-Free, Dermatologist-Approved, Made in USA</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>OFF-DUTY-COMPLEXION--FIXED</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="O2" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P2" s="11" t="inlineStr">
+      <c r="P2" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q2" s="11" t="inlineStr">
+      <c r="Q2" s="12" t="inlineStr">
         <is>
           <t>65.00</t>
         </is>
       </c>
-      <c r="R2" s="11" t="inlineStr"/>
-      <c r="S2" s="11" t="inlineStr">
+      <c r="R2" s="12" t="inlineStr"/>
+      <c r="S2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T2" s="11" t="inlineStr">
+      <c r="T2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U2" s="11" t="inlineStr"/>
-      <c r="V2" s="11" t="inlineStr">
+      <c r="U2" s="12" t="inlineStr"/>
+      <c r="V2" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/2926/6108/files/01-Off-DutyComplexionTrio_PACKSHOT.png?v=1792008852</t>
         </is>
       </c>
-      <c r="W2" s="11" t="inlineStr">
+      <c r="W2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X2" s="11" t="inlineStr">
+      <c r="X2" s="12" t="inlineStr">
         <is>
           <t>Off-Duty Complexion Trio - Tower28Beauty Official Product View</t>
         </is>
       </c>
-      <c r="Y2" s="11" t="inlineStr">
+      <c r="Y2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z2" s="11" t="inlineStr">
+      <c r="Z2" s="12" t="inlineStr">
         <is>
           <t>Off-Duty Complexion Trio | Restorative Daily Formula</t>
         </is>
       </c>
-      <c r="AA2" s="11" t="inlineStr">
+      <c r="AA2" s="12" t="inlineStr">
         <is>
           <t>The  Off-Duty Complexion Trio  by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered</t>
         </is>
       </c>
-      <c r="AB2" s="11" t="inlineStr">
+      <c r="AB2" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="AC2" s="11" t="inlineStr">
+      <c r="AC2" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>wink-wave-mini-duo</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Wink + Wave Mini Duo | Restorative Daily Formula</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Wink + Wave Mini Duo&lt;/strong&gt; by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1288,141 +1339,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Tower28Beauty</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>Clean Beauty, Skincare Essentials, Daily Ritual, Cruelty-Free, Dermatologist-Approved, Made in USA</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>WINK-WAVE-MINI-DUO-FIXED</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="12" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="R3" s="11" t="inlineStr"/>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="R3" s="12" t="inlineStr"/>
+      <c r="S3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T3" s="11" t="inlineStr">
+      <c r="T3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U3" s="11" t="inlineStr"/>
-      <c r="V3" s="11" t="inlineStr">
+      <c r="U3" s="12" t="inlineStr"/>
+      <c r="V3" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/2926/6108/files/01-Wink_WaveMiniDuo_PACKSHOT.png?v=1792009104</t>
         </is>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X3" s="11" t="inlineStr">
+      <c r="X3" s="12" t="inlineStr">
         <is>
           <t>Wink + Wave Mini Duo - Tower28Beauty Official Product View</t>
         </is>
       </c>
-      <c r="Y3" s="11" t="inlineStr">
+      <c r="Y3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z3" s="11" t="inlineStr">
+      <c r="Z3" s="12" t="inlineStr">
         <is>
           <t>Wink + Wave Mini Duo | Restorative Daily Formula</t>
         </is>
       </c>
-      <c r="AA3" s="11" t="inlineStr">
+      <c r="AA3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">The  Wink + Wave Mini Duo  by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to </t>
         </is>
       </c>
-      <c r="AB3" s="11" t="inlineStr">
+      <c r="AB3" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="AC3" s="11" t="inlineStr">
+      <c r="AC3" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>the-fresh-face-set</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>The Fresh Face Set | Restorative Daily Formula</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;The Fresh Face Set&lt;/strong&gt; by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1437,141 +1488,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Tower28Beauty</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>Clean Beauty, Skincare Essentials, Daily Ritual, Cruelty-Free, Dermatologist-Approved, Made in USA</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>THE-FRESH-FACE-SET-FIXED</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr">
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="Q4" s="12" t="inlineStr">
         <is>
           <t>75.00</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr"/>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="R4" s="12" t="inlineStr"/>
+      <c r="S4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T4" s="11" t="inlineStr">
+      <c r="T4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U4" s="11" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr">
+      <c r="U4" s="12" t="inlineStr"/>
+      <c r="V4" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/2926/6108/files/01-TheFreshFaceSet_PACKSHOT.png?v=1792008543</t>
         </is>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X4" s="11" t="inlineStr">
+      <c r="X4" s="12" t="inlineStr">
         <is>
           <t>The Fresh Face Set - Tower28Beauty Official Product View</t>
         </is>
       </c>
-      <c r="Y4" s="11" t="inlineStr">
+      <c r="Y4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z4" s="11" t="inlineStr">
+      <c r="Z4" s="12" t="inlineStr">
         <is>
           <t>The Fresh Face Set | Restorative Daily Formula</t>
         </is>
       </c>
-      <c r="AA4" s="11" t="inlineStr">
+      <c r="AA4" s="12" t="inlineStr">
         <is>
           <t>The  The Fresh Face Set  by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to el</t>
         </is>
       </c>
-      <c r="AB4" s="11" t="inlineStr">
+      <c r="AB4" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="AC4" s="11" t="inlineStr">
+      <c r="AC4" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>jell-o-x-tower-28-red-shine-on-bag</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>JELL-O® x TOWER 28 RED SHINE-ON BAG | Restorative Daily Formula</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;JELL-O® x TOWER 28 RED SHINE-ON BAG&lt;/strong&gt; by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1586,141 +1637,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Tower28Beauty</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>Clean Beauty, Skincare Essentials, Daily Ritual, Cruelty-Free, Dermatologist-Approved, Made in USA</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>JELL-O-X-TOWER-28-RE-FIXED</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="12" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="R5" s="12" t="inlineStr"/>
+      <c r="S5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T5" s="11" t="inlineStr">
+      <c r="T5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U5" s="11" t="inlineStr"/>
-      <c r="V5" s="11" t="inlineStr">
+      <c r="U5" s="12" t="inlineStr"/>
+      <c r="V5" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/2926/6108/files/260805_Tower-28-PDP_Red-Pouch_001LowRescopy.png?v=1791561950</t>
         </is>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X5" s="11" t="inlineStr">
+      <c r="X5" s="12" t="inlineStr">
         <is>
           <t>JELL-O® x TOWER 28 RED SHINE-ON BAG - Tower28Beauty Official Product View</t>
         </is>
       </c>
-      <c r="Y5" s="11" t="inlineStr">
+      <c r="Y5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z5" s="11" t="inlineStr">
+      <c r="Z5" s="12" t="inlineStr">
         <is>
           <t>JELL-O® x TOWER 28 RED SHINE-ON BAG | Restorative Daily Formula</t>
         </is>
       </c>
-      <c r="AA5" s="11" t="inlineStr">
+      <c r="AA5" s="12" t="inlineStr">
         <is>
           <t>The  JELL-O® x TOWER 28 RED SHINE-ON BAG  by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully</t>
         </is>
       </c>
-      <c r="AB5" s="11" t="inlineStr">
+      <c r="AB5" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="AC5" s="11" t="inlineStr">
+      <c r="AC5" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>so-juicy-jell-o®-x-tower-28-bag-charm</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>So Juicy JELL-O® x Tower 28 Bag Charm | Restorative Daily Formula</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;So Juicy JELL-O® x Tower 28 Bag Charm&lt;/strong&gt; by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1735,124 +1786,124 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Tower28Beauty</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Clean Beauty, Skincare Essentials, Daily Ritual, Cruelty-Free, Dermatologist-Approved, Made in USA</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>SO-JUICY-JELL-O®-X-T-FIXED</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="12" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="R6" s="11" t="inlineStr"/>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="R6" s="12" t="inlineStr"/>
+      <c r="S6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T6" s="11" t="inlineStr">
+      <c r="T6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U6" s="11" t="inlineStr"/>
-      <c r="V6" s="11" t="inlineStr">
+      <c r="U6" s="12" t="inlineStr"/>
+      <c r="V6" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/2926/6108/files/260805_Tower-28-PDP_Fruit-Keychain_001LowRescopy.png?v=1791562034</t>
         </is>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X6" s="11" t="inlineStr">
+      <c r="X6" s="12" t="inlineStr">
         <is>
           <t>So Juicy JELL-O® x Tower 28 Bag Charm - Tower28Beauty Official Product View</t>
         </is>
       </c>
-      <c r="Y6" s="11" t="inlineStr">
+      <c r="Y6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z6" s="11" t="inlineStr">
+      <c r="Z6" s="12" t="inlineStr">
         <is>
           <t>So Juicy JELL-O® x Tower 28 Bag Charm | Restorative Daily Formula</t>
         </is>
       </c>
-      <c r="AA6" s="11" t="inlineStr">
+      <c r="AA6" s="12" t="inlineStr">
         <is>
           <t>The  So Juicy JELL-O® x Tower 28 Bag Charm  by Tower28Beauty represents the highest standard of intentional craftsmanship and functional design. Thoughtful</t>
         </is>
       </c>
-      <c r="AB6" s="11" t="inlineStr">
+      <c r="AB6" s="12" t="inlineStr">
         <is>
           <t>Health &amp; Beauty &gt; Personal Care &gt; Cosmetics &gt; Skin Care</t>
         </is>
       </c>
-      <c r="AC6" s="11" t="inlineStr">
+      <c r="AC6" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
